--- a/Results/Main results/Main results regionalisation.xlsx
+++ b/Results/Main results/Main results regionalisation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Results\Main results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Main results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88AE9F71-6999-440E-BBA5-325B76562F47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DB9A7C-4E50-4123-9AAE-7672EE8CE9CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13380" activeTab="2" xr2:uid="{8B762EDB-2E58-479B-A8DC-3D070ED03EC9}"/>
   </bookViews>
@@ -2020,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1041219A-1CFA-4B29-9344-B05878163749}">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="235.5546875" bestFit="1" customWidth="1"/>
@@ -2762,6 +2762,32 @@
         <v>217.49874256232243</v>
       </c>
     </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>-0.84955861837746893</v>
+      </c>
+      <c r="C13">
+        <v>-0.61823622845561277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>-0.99237845448159656</v>
+      </c>
+      <c r="C14">
+        <v>-0.87540812914845312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <f>(B13-B14)/B13*100</f>
+        <v>-16.811063182066512</v>
+      </c>
+      <c r="C15">
+        <f>(C13-C14)/C13*100</f>
+        <v>-41.597675590003767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
